--- a/JsonConverter/ExcelFiles/WorkData.xlsx
+++ b/JsonConverter/ExcelFiles/WorkData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="37">
   <si>
     <t>데이터 id</t>
   </si>
@@ -41,6 +41,9 @@
     <t>미니게임 여부</t>
   </si>
   <si>
+    <t>필요 에너지</t>
+  </si>
+  <si>
     <t>작업 완료 시간(s)</t>
   </si>
   <si>
@@ -62,12 +65,12 @@
     <t>WorkType</t>
   </si>
   <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>float</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
@@ -75,6 +78,9 @@
   </si>
   <si>
     <t>MiniGame</t>
+  </si>
+  <si>
+    <t>ReqEnergy</t>
   </si>
   <si>
     <t>DurationSeconds</t>
@@ -1154,19 +1160,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="19.3425925925926" customWidth="1"/>
     <col min="2" max="3" width="18.4444444444444" customWidth="1"/>
     <col min="4" max="4" width="17.3333333333333" customWidth="1"/>
-    <col min="5" max="6" width="15.8888888888889" customWidth="1"/>
-    <col min="7" max="7" width="13.5925925925926" customWidth="1"/>
-    <col min="8" max="8" width="19.3518518518519" customWidth="1"/>
-    <col min="9" max="9" width="16.3425925925926" customWidth="1"/>
+    <col min="5" max="5" width="13.3333333333333" customWidth="1"/>
+    <col min="6" max="7" width="15.8888888888889" customWidth="1"/>
+    <col min="8" max="8" width="13.5925925925926" customWidth="1"/>
+    <col min="9" max="9" width="19.3518518518519" customWidth="1"/>
+    <col min="10" max="10" width="16.3425925925926" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:9">
+    <row r="1" ht="18" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1185,7 +1192,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
@@ -1194,221 +1201,245 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" ht="18" spans="1:9">
+    <row r="2" ht="18" spans="1:10">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" ht="18" spans="1:10">
+      <c r="A3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" ht="18" spans="1:10">
+      <c r="A4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>50</v>
+      </c>
+      <c r="H4" s="2">
+        <v>3</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" ht="18" spans="1:10">
+      <c r="A5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G5" s="3">
+        <v>100</v>
+      </c>
+      <c r="H5" s="2">
+        <v>5</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" ht="18" spans="1:10">
+      <c r="A6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>3600</v>
+      </c>
+      <c r="G6" s="3">
+        <v>250</v>
+      </c>
+      <c r="H6" s="2">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
     </row>
-    <row r="3" ht="18" spans="1:9">
-      <c r="A3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="6" t="s">
+    <row r="7" ht="18" spans="1:10">
+      <c r="A7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>5400</v>
+      </c>
+      <c r="G7" s="3">
+        <v>420</v>
+      </c>
+      <c r="H7" s="2">
         <v>20</v>
       </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
     </row>
-    <row r="4" ht="18" spans="1:9">
-      <c r="A4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="3">
+    <row r="8" ht="18" spans="1:10">
+      <c r="A8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="1">
         <v>0</v>
       </c>
-      <c r="F4" s="3">
-        <v>50</v>
-      </c>
-      <c r="G4" s="2">
-        <v>3</v>
-      </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
+      <c r="F8" s="3">
+        <v>7200</v>
+      </c>
+      <c r="G8" s="3">
+        <v>600</v>
+      </c>
+      <c r="H8" s="2">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
     </row>
-    <row r="5" ht="18" spans="1:9">
-      <c r="A5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1800</v>
-      </c>
-      <c r="F5" s="3">
-        <v>100</v>
-      </c>
-      <c r="G5" s="2">
-        <v>5</v>
-      </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" ht="18" spans="1:9">
-      <c r="A6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="3">
-        <v>3600</v>
-      </c>
-      <c r="F6" s="3">
-        <v>250</v>
-      </c>
-      <c r="G6" s="2">
-        <v>12</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" ht="18" spans="1:9">
-      <c r="A7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="3">
-        <v>5400</v>
-      </c>
-      <c r="F7" s="3">
-        <v>420</v>
-      </c>
-      <c r="G7" s="2">
-        <v>20</v>
-      </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" ht="18" spans="1:9">
-      <c r="A8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="3">
-        <v>7200</v>
-      </c>
-      <c r="F8" s="3">
-        <v>600</v>
-      </c>
-      <c r="G8" s="2">
-        <v>30</v>
-      </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:10">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:10">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:10">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:10">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:10">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:10">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:10">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>

--- a/JsonConverter/ExcelFiles/WorkData.xlsx
+++ b/JsonConverter/ExcelFiles/WorkData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
   <si>
     <t>데이터 id</t>
   </si>
@@ -108,6 +108,15 @@
   </si>
   <si>
     <t>SubtitleEdit</t>
+  </si>
+  <si>
+    <t>Work_Manual_02</t>
+  </si>
+  <si>
+    <t>Motion Tracking</t>
+  </si>
+  <si>
+    <t>MotionTracking</t>
   </si>
   <si>
     <t>Work_Auto_01</t>
@@ -1160,7 +1169,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="19.3425925925926" customWidth="1"/>
@@ -1170,7 +1179,7 @@
     <col min="6" max="7" width="15.8888888888889" customWidth="1"/>
     <col min="8" max="8" width="13.5925925925926" customWidth="1"/>
     <col min="9" max="9" width="19.3518518518519" customWidth="1"/>
-    <col min="10" max="10" width="16.3425925925926" customWidth="1"/>
+    <col min="10" max="10" width="31.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" spans="1:10">
@@ -1292,7 +1301,7 @@
         <v>50</v>
       </c>
       <c r="H4" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
@@ -1301,118 +1310,141 @@
       <c r="A5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="E5" s="1">
+        <v>3</v>
+      </c>
+      <c r="F5" s="3">
         <v>0</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1800</v>
       </c>
       <c r="G5" s="3">
         <v>100</v>
       </c>
       <c r="H5" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
     </row>
     <row r="6" ht="18" spans="1:10">
       <c r="A6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="3">
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="G6" s="3">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="H6" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
     </row>
     <row r="7" ht="18" spans="1:10">
       <c r="A7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
       </c>
       <c r="F7" s="3">
-        <v>5400</v>
+        <v>3600</v>
       </c>
       <c r="G7" s="3">
-        <v>420</v>
+        <v>250</v>
       </c>
       <c r="H7" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
     </row>
     <row r="8" ht="18" spans="1:10">
       <c r="A8" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
       </c>
       <c r="F8" s="3">
-        <v>7200</v>
+        <v>5400</v>
       </c>
       <c r="G8" s="3">
-        <v>600</v>
+        <v>420</v>
       </c>
       <c r="H8" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
+    <row r="9" ht="18" spans="1:10">
+      <c r="A9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>7200</v>
+      </c>
+      <c r="G9" s="3">
+        <v>600</v>
+      </c>
+      <c r="H9" s="2">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="8"/>
@@ -1443,6 +1475,11 @@
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/JsonConverter/ExcelFiles/WorkData.xlsx
+++ b/JsonConverter/ExcelFiles/WorkData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="9000" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="시트1" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
-  <si>
-    <t>데이터 id</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="61">
+  <si>
+    <r>
+      <t xml:space="preserve">데이터 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <charset val="134"/>
+      </rPr>
+      <t>id</t>
+    </r>
   </si>
   <si>
     <t>이름</t>
@@ -44,13 +55,64 @@
     <t>필요 에너지</t>
   </si>
   <si>
-    <t>작업 완료 시간(s)</t>
-  </si>
-  <si>
-    <t>보상(돈)</t>
-  </si>
-  <si>
-    <t>보상(DP)</t>
+    <r>
+      <t>작업 완료 시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(s)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>보상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <charset val="134"/>
+      </rPr>
+      <t>돈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>보상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(DP)</t>
+    </r>
   </si>
   <si>
     <t>아이콘 스프라이트</t>
@@ -110,6 +172,9 @@
     <t>SubtitleEdit</t>
   </si>
   <si>
+    <t>자막 편집 업무를 수행합니다</t>
+  </si>
+  <si>
     <t>Work_Manual_02</t>
   </si>
   <si>
@@ -119,6 +184,9 @@
     <t>MotionTracking</t>
   </si>
   <si>
+    <t>모션 캡쳐 알바를 신청합니다</t>
+  </si>
+  <si>
     <t>Work_Auto_01</t>
   </si>
   <si>
@@ -131,22 +199,90 @@
     <t>None</t>
   </si>
   <si>
+    <t>동영상 싱크 조절 업무입니다</t>
+  </si>
+  <si>
     <t>Work_Auto_02</t>
   </si>
   <si>
     <t>Make Thumbnail</t>
   </si>
   <si>
+    <t>영상 썸네일을 그립니다</t>
+  </si>
+  <si>
     <t>Work_Auto_03</t>
   </si>
   <si>
     <t>Encoding</t>
   </si>
   <si>
+    <t>영상 인코딩 업무를 배웁니다</t>
+  </si>
+  <si>
     <t>Work_Auto_04</t>
   </si>
   <si>
-    <t>Backup Video</t>
+    <t>Backup Files</t>
+  </si>
+  <si>
+    <t>자료 백업</t>
+  </si>
+  <si>
+    <t>Work_Auto_05</t>
+  </si>
+  <si>
+    <t>Translate Movie</t>
+  </si>
+  <si>
+    <t>해외 영화를 번역합니다</t>
+  </si>
+  <si>
+    <t>Work_Auto_06</t>
+  </si>
+  <si>
+    <t>Game planning</t>
+  </si>
+  <si>
+    <t>게임 컨텐츠 기획을 실행합니다</t>
+  </si>
+  <si>
+    <t>Work_Gambling_01</t>
+  </si>
+  <si>
+    <t>Scratch Lottery</t>
+  </si>
+  <si>
+    <t>Gamble</t>
+  </si>
+  <si>
+    <t>ScratchLottery</t>
+  </si>
+  <si>
+    <r>
+      <t>즉석 복권 긁기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <charset val="134"/>
+      </rPr>
+      <t>!!</t>
+    </r>
+  </si>
+  <si>
+    <t>Work_Creative_01</t>
+  </si>
+  <si>
+    <t>Write a novel</t>
+  </si>
+  <si>
+    <t>Creative</t>
+  </si>
+  <si>
+    <t>소설 쓰기</t>
   </si>
 </sst>
 </file>
@@ -154,18 +290,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;₩&quot;* #,##0_-;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;₩&quot;* #,##0.00_-;\-&quot;₩&quot;* #,##0.00_-;_-&quot;₩&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -174,18 +309,18 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
+      <name val="Noto Sans KR"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Noto Sans KR"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Noto Sans KR"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -203,6 +338,13 @@
       <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -350,7 +492,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.8"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -664,31 +806,18 @@
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -697,130 +826,131 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="50">
@@ -875,7 +1005,289 @@
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
     <cellStyle name="표준" xfId="49"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00EBF1DE"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -889,10 +1301,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -930,234 +1342,128 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
-                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1175,14 +1481,14 @@
     <col min="1" max="1" width="19.3425925925926" customWidth="1"/>
     <col min="2" max="3" width="18.4444444444444" customWidth="1"/>
     <col min="4" max="4" width="17.3333333333333" customWidth="1"/>
-    <col min="5" max="5" width="13.3333333333333" customWidth="1"/>
+    <col min="5" max="5" width="13.3425925925926" customWidth="1"/>
     <col min="6" max="7" width="15.8888888888889" customWidth="1"/>
-    <col min="8" max="8" width="13.5925925925926" customWidth="1"/>
+    <col min="8" max="8" width="13.6018518518519" customWidth="1"/>
     <col min="9" max="9" width="19.3518518518519" customWidth="1"/>
     <col min="10" max="10" width="31.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:10">
+    <row r="1" ht="17.25" customHeight="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1204,49 +1510,49 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="18" spans="1:10">
-      <c r="A2" s="3" t="s">
+    <row r="2" ht="17.25" customHeight="1" spans="1:10">
+      <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="18" spans="1:10">
+    <row r="3" ht="17.25" customHeight="1" spans="1:10">
       <c r="A3" s="4" t="s">
         <v>14</v>
       </c>
@@ -1268,221 +1574,341 @@
       <c r="G3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" ht="18" spans="1:10">
-      <c r="A4" s="3" t="s">
+    <row r="4" ht="17.25" customHeight="1" spans="1:10">
+      <c r="A4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>0</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>50</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <v>5</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="5" ht="18" spans="1:10">
-      <c r="A5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="5" ht="17.25" customHeight="1" spans="1:10">
+      <c r="A5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="B5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>29</v>
+      <c r="D5" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="E5" s="1">
         <v>3</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>0</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>100</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <v>8</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="6" ht="18" spans="1:10">
-      <c r="A6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="3" t="s">
+    <row r="6" ht="17.25" customHeight="1" spans="1:10">
+      <c r="A6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="B6" s="3" t="s">
         <v>33</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>1800</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2">
         <v>100</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <v>5</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="7" ht="18" spans="1:10">
-      <c r="A7" s="3" t="s">
+    <row r="7" ht="17.25" customHeight="1" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="D7" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <v>3600</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2">
         <v>250</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <v>12</v>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="8" ht="18" spans="1:10">
-      <c r="A8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>33</v>
+    <row r="8" ht="17.25" customHeight="1" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <v>5400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="2">
         <v>420</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="1">
         <v>20</v>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="9" ht="18" spans="1:10">
-      <c r="A9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>33</v>
+    <row r="9" ht="17.25" customHeight="1" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <v>7200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="2">
         <v>600</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="1">
         <v>30</v>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
+    <row r="10" ht="17.25" customHeight="1" spans="1:10">
+      <c r="A10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>9600</v>
+      </c>
+      <c r="G10" s="1">
+        <v>800</v>
+      </c>
+      <c r="H10" s="1">
+        <v>40</v>
+      </c>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
+    <row r="11" ht="17.25" customHeight="1" spans="1:10">
+      <c r="A11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
+        <v>10800</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H11" s="1">
+        <v>50</v>
+      </c>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
+    <row r="12" ht="17.25" customHeight="1" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="1">
+        <v>10</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>56</v>
+      </c>
     </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
+    <row r="13" ht="17.25" customHeight="1" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>10</v>
+      </c>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
+    <row r="14" ht="17.25" customHeight="1" spans="1:10">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/WorkData.xlsx
+++ b/JsonConverter/ExcelFiles/WorkData.xlsx
@@ -30,6 +30,12 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="61">
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">데이터 </t>
     </r>
     <r>
@@ -56,6 +62,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <charset val="134"/>
+      </rPr>
       <t>작업 완료 시간</t>
     </r>
     <r>
@@ -70,6 +82,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <charset val="134"/>
+      </rPr>
       <t>보상</t>
     </r>
     <r>
@@ -102,6 +120,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <charset val="134"/>
+      </rPr>
       <t>보상</t>
     </r>
     <r>
@@ -260,6 +284,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <charset val="134"/>
+      </rPr>
       <t>즉석 복권 긁기</t>
     </r>
     <r>
@@ -295,7 +325,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;₩&quot;* #,##0.00_-;\-&quot;₩&quot;* #,##0.00_-;_-&quot;₩&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -310,12 +340,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Noto Sans KR"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Noto Sans KR"/>
       <charset val="134"/>
     </font>
@@ -806,18 +830,21 @@
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -826,132 +853,128 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1530,10 +1553,10 @@
       <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -1542,45 +1565,45 @@
       <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1" spans="1:10">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="4" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1588,17 +1611,17 @@
       <c r="A4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E4" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
@@ -1618,17 +1641,17 @@
       <c r="A5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E5" s="1">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
@@ -1648,13 +1671,13 @@
       <c r="A6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E6" s="1">
@@ -1678,13 +1701,13 @@
       <c r="A7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E7" s="1">
@@ -1708,13 +1731,13 @@
       <c r="A8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E8" s="1">
@@ -1738,13 +1761,13 @@
       <c r="A9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E9" s="1">
@@ -1765,16 +1788,16 @@
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1" spans="1:10">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E10" s="1">
@@ -1795,7 +1818,7 @@
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1" spans="1:10">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -1804,7 +1827,7 @@
       <c r="C11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E11" s="1">
@@ -1834,11 +1857,11 @@
       <c r="C12" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E12" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -1864,7 +1887,7 @@
       <c r="C13" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E13" s="1">
@@ -1897,14 +1920,14 @@
       <c r="J14" s="1"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/JsonConverter/ExcelFiles/WorkData.xlsx
+++ b/JsonConverter/ExcelFiles/WorkData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="59">
   <si>
     <r>
       <rPr>
@@ -211,6 +211,30 @@
     <t>모션 캡쳐 알바를 신청합니다</t>
   </si>
   <si>
+    <t>Work_Manual_03</t>
+  </si>
+  <si>
+    <t>Roll Dice</t>
+  </si>
+  <si>
+    <t>DiceGamble</t>
+  </si>
+  <si>
+    <t>주사위 굴리기!!</t>
+  </si>
+  <si>
+    <t>Work_Manual_04</t>
+  </si>
+  <si>
+    <t>Write a novel</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>소설 쓰기</t>
+  </si>
+  <si>
     <t>Work_Auto_01</t>
   </si>
   <si>
@@ -220,9 +244,6 @@
     <t>Auto</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
     <t>동영상 싱크 조절 업무입니다</t>
   </si>
   <si>
@@ -269,50 +290,6 @@
   </si>
   <si>
     <t>게임 컨텐츠 기획을 실행합니다</t>
-  </si>
-  <si>
-    <t>Work_Gambling_01</t>
-  </si>
-  <si>
-    <t>Scratch Lottery</t>
-  </si>
-  <si>
-    <t>Gamble</t>
-  </si>
-  <si>
-    <t>ScratchLottery</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <charset val="134"/>
-      </rPr>
-      <t>즉석 복권 긁기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <charset val="134"/>
-      </rPr>
-      <t>!!</t>
-    </r>
-  </si>
-  <si>
-    <t>Work_Creative_01</t>
-  </si>
-  <si>
-    <t>Write a novel</t>
-  </si>
-  <si>
-    <t>Creative</t>
-  </si>
-  <si>
-    <t>소설 쓰기</t>
   </si>
 </sst>
 </file>
@@ -1498,7 +1475,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="19.3425925925926" customWidth="1"/>
@@ -1671,56 +1648,56 @@
       <c r="A6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="E6" s="1">
+        <v>20</v>
+      </c>
+      <c r="F6" s="1">
         <v>0</v>
       </c>
-      <c r="F6" s="2">
-        <v>1800</v>
-      </c>
-      <c r="G6" s="2">
-        <v>100</v>
+      <c r="G6" s="1">
+        <v>2000</v>
       </c>
       <c r="H6" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1" spans="1:10">
       <c r="A7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
         <v>0</v>
       </c>
-      <c r="F7" s="2">
-        <v>3600</v>
-      </c>
-      <c r="G7" s="2">
-        <v>250</v>
+      <c r="G7" s="1">
+        <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1" t="s">
@@ -1735,199 +1712,199 @@
         <v>41</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>5400</v>
+        <v>1800</v>
       </c>
       <c r="G8" s="2">
-        <v>420</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
       <c r="F9" s="2">
-        <v>7200</v>
+        <v>3600</v>
       </c>
       <c r="G9" s="2">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="H9" s="1">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1" spans="1:10">
-      <c r="A10" s="1" t="s">
-        <v>46</v>
+      <c r="A10" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>34</v>
+        <v>48</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
       </c>
-      <c r="F10" s="1">
-        <v>9600</v>
-      </c>
-      <c r="G10" s="1">
-        <v>800</v>
+      <c r="F10" s="2">
+        <v>5400</v>
+      </c>
+      <c r="G10" s="2">
+        <v>420</v>
       </c>
       <c r="H10" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1" spans="1:10">
-      <c r="A11" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="2" t="s">
         <v>50</v>
       </c>
+      <c r="B11" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="C11" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
-      <c r="F11" s="1">
-        <v>10800</v>
-      </c>
-      <c r="G11" s="1">
-        <v>1000</v>
+      <c r="F11" s="2">
+        <v>7200</v>
+      </c>
+      <c r="G11" s="2">
+        <v>600</v>
       </c>
       <c r="H11" s="1">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>54</v>
       </c>
+      <c r="C12" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="D12" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="E12" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F12" s="1">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="G12" s="1">
-        <v>2000</v>
+        <v>800</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1" spans="1:10">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="C13" s="2" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="1">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H13" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
-    <row r="14" ht="17.25" customHeight="1" spans="1:10">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
+    <row r="16" ht="17.25" customHeight="1" spans="1:10">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
     </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
+    <row r="17" spans="1:3">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
     </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
+    <row r="18" spans="1:3">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/JsonConverter/ExcelFiles/WorkData.xlsx
+++ b/JsonConverter/ExcelFiles/WorkData.xlsx
@@ -232,7 +232,7 @@
     <t>None</t>
   </si>
   <si>
-    <t>소설 쓰기</t>
+    <t>소설 쓰기(미구현)</t>
   </si>
   <si>
     <t>Work_Auto_01</t>

--- a/JsonConverter/ExcelFiles/WorkData.xlsx
+++ b/JsonConverter/ExcelFiles/WorkData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" tabRatio="500"/>
+    <workbookView windowWidth="13488" windowHeight="8964" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="시트1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="69">
   <si>
     <r>
       <rPr>
@@ -196,6 +196,9 @@
     <t>SubtitleEdit</t>
   </si>
   <si>
+    <t>Sprites/Icon_Work[Icon_Work_0]</t>
+  </si>
+  <si>
     <t>자막 편집 업무를 수행합니다</t>
   </si>
   <si>
@@ -208,6 +211,9 @@
     <t>MotionTracking</t>
   </si>
   <si>
+    <t>Sprites/Icon_Work[Icon_Work_1]</t>
+  </si>
+  <si>
     <t>모션 캡쳐 알바를 신청합니다</t>
   </si>
   <si>
@@ -220,6 +226,9 @@
     <t>DiceGamble</t>
   </si>
   <si>
+    <t>Sprites/Icon_Work[Icon_Work_2]</t>
+  </si>
+  <si>
     <t>주사위 굴리기!!</t>
   </si>
   <si>
@@ -232,6 +241,9 @@
     <t>None</t>
   </si>
   <si>
+    <t>Sprites/Icon_Work[Icon_Work_3]</t>
+  </si>
+  <si>
     <t>소설 쓰기(미구현)</t>
   </si>
   <si>
@@ -244,6 +256,9 @@
     <t>Auto</t>
   </si>
   <si>
+    <t>Sprites/Icon_Work[Icon_Work_4]</t>
+  </si>
+  <si>
     <t>동영상 싱크 조절 업무입니다</t>
   </si>
   <si>
@@ -253,6 +268,9 @@
     <t>Make Thumbnail</t>
   </si>
   <si>
+    <t>Sprites/Icon_Work[Icon_Work_5]</t>
+  </si>
+  <si>
     <t>영상 썸네일을 그립니다</t>
   </si>
   <si>
@@ -262,6 +280,9 @@
     <t>Encoding</t>
   </si>
   <si>
+    <t>Sprites/Icon_Work[Icon_Work_6]</t>
+  </si>
+  <si>
     <t>영상 인코딩 업무를 배웁니다</t>
   </si>
   <si>
@@ -271,6 +292,9 @@
     <t>Backup Files</t>
   </si>
   <si>
+    <t>Sprites/Icon_Work[Icon_Work_7]</t>
+  </si>
+  <si>
     <t>자료 백업</t>
   </si>
   <si>
@@ -280,6 +304,9 @@
     <t>Translate Movie</t>
   </si>
   <si>
+    <t>Sprites/Icon_Work[Icon_Work_8]</t>
+  </si>
+  <si>
     <t>해외 영화를 번역합니다</t>
   </si>
   <si>
@@ -287,6 +314,9 @@
   </si>
   <si>
     <t>Game planning</t>
+  </si>
+  <si>
+    <t>Sprites/Icon_Work[Icon_Work_9]</t>
   </si>
   <si>
     <t>게임 컨텐츠 기획을 실행합니다</t>
@@ -1484,7 +1514,7 @@
     <col min="5" max="5" width="13.3425925925926" customWidth="1"/>
     <col min="6" max="7" width="15.8888888888889" customWidth="1"/>
     <col min="8" max="8" width="13.6018518518519" customWidth="1"/>
-    <col min="9" max="9" width="19.3518518518519" customWidth="1"/>
+    <col min="9" max="9" width="37.5185185185185" customWidth="1"/>
     <col min="10" max="10" width="31.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1609,23 +1639,25 @@
       <c r="H4" s="1">
         <v>5</v>
       </c>
-      <c r="I4" s="1"/>
+      <c r="I4" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="J4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" s="1">
         <v>25</v>
@@ -1639,23 +1671,25 @@
       <c r="H5" s="1">
         <v>8</v>
       </c>
-      <c r="I5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J5" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E6" s="1">
         <v>20</v>
@@ -1669,23 +1703,25 @@
       <c r="H6" s="1">
         <v>0</v>
       </c>
-      <c r="I6" s="1"/>
+      <c r="I6" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="J6" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -1699,23 +1735,25 @@
       <c r="H7" s="1">
         <v>10</v>
       </c>
-      <c r="I7" s="1"/>
+      <c r="I7" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="J7" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
@@ -1729,23 +1767,25 @@
       <c r="H8" s="1">
         <v>5</v>
       </c>
-      <c r="I8" s="1"/>
+      <c r="I8" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J8" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
@@ -1759,23 +1799,25 @@
       <c r="H9" s="1">
         <v>12</v>
       </c>
-      <c r="I9" s="1"/>
+      <c r="I9" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="J9" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
@@ -1789,23 +1831,25 @@
       <c r="H10" s="1">
         <v>20</v>
       </c>
-      <c r="I10" s="1"/>
+      <c r="I10" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="J10" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
@@ -1819,23 +1863,25 @@
       <c r="H11" s="1">
         <v>30</v>
       </c>
-      <c r="I11" s="1"/>
+      <c r="I11" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="J11" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
@@ -1849,23 +1895,25 @@
       <c r="H12" s="1">
         <v>40</v>
       </c>
-      <c r="I12" s="1"/>
+      <c r="I12" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="J12" s="1" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
@@ -1879,9 +1927,11 @@
       <c r="H13" s="1">
         <v>50</v>
       </c>
-      <c r="I13" s="1"/>
+      <c r="I13" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J13" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1" spans="1:10">

--- a/JsonConverter/ExcelFiles/WorkData.xlsx
+++ b/JsonConverter/ExcelFiles/WorkData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
   <si>
     <r>
       <rPr>
@@ -223,22 +223,25 @@
     <t>Write a novel</t>
   </si>
   <si>
+    <t>NovelWriting</t>
+  </si>
+  <si>
+    <t>Sprites/Icon_Work[Icon_Work_3]</t>
+  </si>
+  <si>
+    <t>소설 쓰기</t>
+  </si>
+  <si>
+    <t>Work_Auto_01</t>
+  </si>
+  <si>
+    <t>Sync Subtitle</t>
+  </si>
+  <si>
+    <t>Auto</t>
+  </si>
+  <si>
     <t>None</t>
-  </si>
-  <si>
-    <t>Sprites/Icon_Work[Icon_Work_3]</t>
-  </si>
-  <si>
-    <t>소설 쓰기</t>
-  </si>
-  <si>
-    <t>Work_Auto_01</t>
-  </si>
-  <si>
-    <t>Sync Subtitle</t>
-  </si>
-  <si>
-    <t>Auto</t>
   </si>
   <si>
     <t>Sprites/Icon_Work[Icon_Work_4]</t>
@@ -827,7 +830,7 @@
       <c r="C7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E7" s="1">
@@ -863,7 +866,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E8" s="1">
         <v>0.0</v>
@@ -881,24 +884,24 @@
         <v>5.0</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E9" s="1">
         <v>0.0</v>
@@ -916,24 +919,24 @@
         <v>12.0</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E10" s="1">
         <v>0.0</v>
@@ -951,24 +954,24 @@
         <v>20.0</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E11" s="1">
         <v>0.0</v>
@@ -986,24 +989,24 @@
         <v>30.0</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E12" s="1">
         <v>0.0</v>
@@ -1021,24 +1024,24 @@
         <v>40.0</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E13" s="1">
         <v>0.0</v>
@@ -1056,10 +1059,10 @@
         <v>50.0</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/WorkData.xlsx
+++ b/JsonConverter/ExcelFiles/WorkData.xlsx
@@ -807,8 +807,8 @@
       <c r="G6" s="1">
         <v>0.0</v>
       </c>
-      <c r="H6" s="1">
-        <v>2000.0</v>
+      <c r="H6" s="2">
+        <v>400.0</v>
       </c>
       <c r="I6" s="1">
         <v>0.0</v>
